--- a/templates/forms/CarePlan_Info_Request.xlsx
+++ b/templates/forms/CarePlan_Info_Request.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\CareManagementTool\templates\forms\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{4E848AAB-5619-45B7-94F3-6EC50A3D9472}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{993B773D-30CB-4B04-B10F-D199F45EDE60}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2985" yWindow="2985" windowWidth="10635" windowHeight="10725" xr2:uid="{CF2C2649-58DB-4726-BA5D-5E10CE473C98}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{CF2C2649-58DB-4726-BA5D-5E10CE473C98}"/>
   </bookViews>
   <sheets>
     <sheet name="資料提供申請書" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="41">
   <si>
     <t>介護サービス計画作成に係る資料提供申請書</t>
     <rPh sb="0" eb="2">
@@ -698,98 +698,6 @@
     </rPh>
     <rPh sb="35" eb="37">
       <t>チュウイ</t>
-    </rPh>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>居宅介護支援事業所　安濃津ろまん</t>
-    <rPh sb="0" eb="16">
-      <t>キ</t>
-    </rPh>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>059-253-6599</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>介護支援専門員</t>
-    <rPh sb="0" eb="2">
-      <t>カイゴ</t>
-    </rPh>
-    <rPh sb="2" eb="4">
-      <t>シエン</t>
-    </rPh>
-    <rPh sb="4" eb="7">
-      <t>センモンイン</t>
-    </rPh>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>倉野　美和</t>
-    <rPh sb="0" eb="2">
-      <t>クラノ</t>
-    </rPh>
-    <rPh sb="3" eb="5">
-      <t>ミワ</t>
-    </rPh>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>山川　和輝</t>
-    <rPh sb="0" eb="2">
-      <t>ヤマカワ</t>
-    </rPh>
-    <rPh sb="3" eb="5">
-      <t>カズテル</t>
-    </rPh>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>令和　 7年　11月　  日</t>
-    <rPh sb="0" eb="1">
-      <t>レイ</t>
-    </rPh>
-    <rPh sb="1" eb="2">
-      <t>ワ</t>
-    </rPh>
-    <rPh sb="5" eb="6">
-      <t>ネン</t>
-    </rPh>
-    <rPh sb="9" eb="10">
-      <t>ツキ</t>
-    </rPh>
-    <rPh sb="13" eb="14">
-      <t>ニチ</t>
-    </rPh>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>津市新町2丁目7-45</t>
-    <rPh sb="0" eb="2">
-      <t>ツシ</t>
-    </rPh>
-    <rPh sb="2" eb="4">
-      <t>シンマチ</t>
-    </rPh>
-    <rPh sb="5" eb="7">
-      <t>チョウメ</t>
-    </rPh>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>昭和 6年8月1日</t>
-    <rPh sb="0" eb="2">
-      <t>ショウワ</t>
-    </rPh>
-    <rPh sb="4" eb="5">
-      <t>ネン</t>
-    </rPh>
-    <rPh sb="6" eb="7">
-      <t>ガツ</t>
-    </rPh>
-    <rPh sb="8" eb="9">
-      <t>ニチ</t>
     </rPh>
     <phoneticPr fontId="2"/>
   </si>
@@ -798,6 +706,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="1">
+    <numFmt numFmtId="177" formatCode="[$]ggge&quot;年&quot;m&quot;月&quot;d&quot;日&quot;;@" x16r2:formatCode16="[$-ja-JP-x-gannen]ggge&quot;年&quot;m&quot;月&quot;d&quot;日&quot;;@"/>
+  </numFmts>
   <fonts count="21" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -1927,8 +1838,8 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="71">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
+  <cellXfs count="70">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -1953,9 +1864,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -2001,6 +1909,15 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="distributed"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2013,15 +1930,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="33" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="34" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2058,10 +1966,31 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="41" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="58" fontId="0" fillId="0" borderId="26" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="58" fontId="0" fillId="0" borderId="27" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
@@ -2082,33 +2011,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2138,6 +2040,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="26" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="27" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="42">
@@ -2545,7 +2453,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{05E88732-8E50-4485-B520-0C779539F7EA}">
-  <dimension ref="A1:G44"/>
+  <dimension ref="A1:F44"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="2" width="14.875" style="1" customWidth="1"/>
@@ -2557,19 +2465,17 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="F1" s="2" t="s">
-        <v>46</v>
-      </c>
+      <c r="F1" s="2"/>
     </row>
     <row r="3" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A3" s="61" t="s">
+      <c r="A3" s="58" t="s">
         <v>0</v>
       </c>
-      <c r="B3" s="61"/>
-      <c r="C3" s="61"/>
-      <c r="D3" s="61"/>
-      <c r="E3" s="61"/>
-      <c r="F3" s="61"/>
+      <c r="B3" s="58"/>
+      <c r="C3" s="58"/>
+      <c r="D3" s="58"/>
+      <c r="E3" s="58"/>
+      <c r="F3" s="58"/>
     </row>
     <row r="4" spans="1:6" ht="12" customHeight="1" x14ac:dyDescent="0.15"/>
     <row r="5" spans="1:6" x14ac:dyDescent="0.15">
@@ -2585,34 +2491,28 @@
     </row>
     <row r="8" spans="1:6" ht="5.0999999999999996" customHeight="1" x14ac:dyDescent="0.15"/>
     <row r="9" spans="1:6" ht="26.45" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="C9" s="23" t="s">
+      <c r="C9" s="22" t="s">
         <v>37</v>
       </c>
-      <c r="D9" s="55" t="s">
-        <v>41</v>
-      </c>
-      <c r="E9" s="55"/>
-      <c r="F9" s="55"/>
+      <c r="D9" s="46"/>
+      <c r="E9" s="46"/>
+      <c r="F9" s="46"/>
     </row>
     <row r="10" spans="1:6" ht="26.45" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="C10" s="20" t="s">
+      <c r="C10" s="19" t="s">
         <v>1</v>
       </c>
-      <c r="D10" s="55" t="s">
-        <v>44</v>
-      </c>
-      <c r="E10" s="55"/>
-      <c r="F10" s="55"/>
+      <c r="D10" s="46"/>
+      <c r="E10" s="46"/>
+      <c r="F10" s="46"/>
     </row>
     <row r="11" spans="1:6" ht="26.45" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="C11" s="24" t="s">
+      <c r="C11" s="23" t="s">
         <v>2</v>
       </c>
-      <c r="D11" s="55" t="s">
-        <v>42</v>
-      </c>
-      <c r="E11" s="55"/>
-      <c r="F11" s="55"/>
+      <c r="D11" s="46"/>
+      <c r="E11" s="46"/>
+      <c r="F11" s="46"/>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A13" s="1" t="s">
@@ -2620,277 +2520,262 @@
       </c>
     </row>
     <row r="15" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A15" s="62" t="s">
+      <c r="A15" s="59" t="s">
         <v>3</v>
       </c>
-      <c r="B15" s="63"/>
-      <c r="C15" s="69" t="s">
+      <c r="B15" s="60"/>
+      <c r="C15" s="66" t="s">
         <v>4</v>
       </c>
-      <c r="D15" s="69"/>
-      <c r="E15" s="69"/>
-      <c r="F15" s="70"/>
+      <c r="D15" s="66"/>
+      <c r="E15" s="66"/>
+      <c r="F15" s="67"/>
     </row>
     <row r="16" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A16" s="64"/>
-      <c r="B16" s="65"/>
-      <c r="C16" s="46" t="s">
+      <c r="A16" s="61"/>
+      <c r="B16" s="62"/>
+      <c r="C16" s="52" t="s">
         <v>5</v>
       </c>
-      <c r="D16" s="46"/>
-      <c r="E16" s="46"/>
-      <c r="F16" s="47"/>
+      <c r="D16" s="52"/>
+      <c r="E16" s="52"/>
+      <c r="F16" s="53"/>
     </row>
     <row r="17" spans="1:6" ht="27" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A17" s="66" t="s">
+      <c r="A17" s="63" t="s">
         <v>25</v>
       </c>
-      <c r="B17" s="67"/>
-      <c r="C17" s="48" t="s">
+      <c r="B17" s="64"/>
+      <c r="C17" s="54" t="s">
         <v>35</v>
       </c>
-      <c r="D17" s="49"/>
-      <c r="E17" s="49"/>
-      <c r="F17" s="50"/>
+      <c r="D17" s="55"/>
+      <c r="E17" s="55"/>
+      <c r="F17" s="56"/>
     </row>
     <row r="18" spans="1:6" ht="27" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A18" s="62" t="s">
+      <c r="A18" s="59" t="s">
         <v>6</v>
       </c>
-      <c r="B18" s="11" t="s">
+      <c r="B18" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="C18" s="25" t="s">
-        <v>45</v>
-      </c>
-      <c r="D18" s="25"/>
-      <c r="E18" s="25"/>
-      <c r="F18" s="51"/>
+      <c r="C18" s="27"/>
+      <c r="D18" s="27"/>
+      <c r="E18" s="27"/>
+      <c r="F18" s="57"/>
     </row>
     <row r="19" spans="1:6" ht="27" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A19" s="68"/>
-      <c r="B19" s="12" t="s">
+      <c r="A19" s="65"/>
+      <c r="B19" s="11" t="s">
         <v>8</v>
       </c>
-      <c r="C19" s="59" t="s">
-        <v>43</v>
-      </c>
-      <c r="D19" s="59"/>
-      <c r="E19" s="59"/>
-      <c r="F19" s="60"/>
+      <c r="C19" s="50"/>
+      <c r="D19" s="50"/>
+      <c r="E19" s="50"/>
+      <c r="F19" s="51"/>
     </row>
     <row r="20" spans="1:6" ht="27" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A20" s="38" t="s">
+      <c r="A20" s="37" t="s">
         <v>36</v>
       </c>
-      <c r="B20" s="13" t="s">
+      <c r="B20" s="12" t="s">
         <v>9</v>
       </c>
-      <c r="C20" s="41" t="s">
-        <v>47</v>
-      </c>
-      <c r="D20" s="42"/>
-      <c r="E20" s="42"/>
-      <c r="F20" s="43"/>
+      <c r="C20" s="40"/>
+      <c r="D20" s="41"/>
+      <c r="E20" s="41"/>
+      <c r="F20" s="42"/>
     </row>
     <row r="21" spans="1:6" ht="27" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A21" s="39"/>
-      <c r="B21" s="14" t="s">
+      <c r="A21" s="38"/>
+      <c r="B21" s="13" t="s">
         <v>10</v>
       </c>
-      <c r="C21" s="44" t="s">
-        <v>48</v>
-      </c>
-      <c r="D21" s="45"/>
-      <c r="E21" s="14" t="s">
+      <c r="C21" s="68"/>
+      <c r="D21" s="69"/>
+      <c r="E21" s="13" t="s">
         <v>26</v>
       </c>
-      <c r="F21" s="15">
-        <v>2010007726</v>
-      </c>
+      <c r="F21" s="14"/>
     </row>
     <row r="22" spans="1:6" ht="27" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A22" s="39"/>
-      <c r="B22" s="56" t="s">
+      <c r="A22" s="38"/>
+      <c r="B22" s="47" t="s">
         <v>11</v>
       </c>
-      <c r="C22" s="56"/>
-      <c r="D22" s="57"/>
-      <c r="E22" s="57"/>
-      <c r="F22" s="58"/>
+      <c r="C22" s="47"/>
+      <c r="D22" s="48"/>
+      <c r="E22" s="48"/>
+      <c r="F22" s="49"/>
     </row>
     <row r="23" spans="1:6" ht="27" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A23" s="40"/>
-      <c r="B23" s="16"/>
-      <c r="C23" s="17"/>
-      <c r="D23" s="18" t="s">
+      <c r="A23" s="39"/>
+      <c r="B23" s="15"/>
+      <c r="C23" s="16"/>
+      <c r="D23" s="17" t="s">
         <v>7</v>
       </c>
-      <c r="E23" s="27"/>
-      <c r="F23" s="28"/>
+      <c r="E23" s="29"/>
+      <c r="F23" s="30"/>
     </row>
     <row r="24" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A24" s="35" t="s">
+      <c r="A24" s="34" t="s">
         <v>12</v>
       </c>
-      <c r="B24" s="36"/>
-      <c r="C24" s="36"/>
-      <c r="D24" s="36"/>
-      <c r="E24" s="36"/>
-      <c r="F24" s="37"/>
+      <c r="B24" s="35"/>
+      <c r="C24" s="35"/>
+      <c r="D24" s="35"/>
+      <c r="E24" s="35"/>
+      <c r="F24" s="36"/>
     </row>
     <row r="25" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A25" s="29" t="s">
+      <c r="A25" s="24" t="s">
         <v>13</v>
       </c>
-      <c r="B25" s="30"/>
-      <c r="C25" s="30"/>
-      <c r="D25" s="30"/>
-      <c r="E25" s="30"/>
-      <c r="F25" s="31"/>
+      <c r="B25" s="25"/>
+      <c r="C25" s="25"/>
+      <c r="D25" s="25"/>
+      <c r="E25" s="25"/>
+      <c r="F25" s="26"/>
     </row>
     <row r="26" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A26" s="29" t="s">
+      <c r="A26" s="24" t="s">
         <v>14</v>
       </c>
-      <c r="B26" s="30"/>
-      <c r="C26" s="30"/>
-      <c r="D26" s="30"/>
-      <c r="E26" s="30"/>
-      <c r="F26" s="31"/>
+      <c r="B26" s="25"/>
+      <c r="C26" s="25"/>
+      <c r="D26" s="25"/>
+      <c r="E26" s="25"/>
+      <c r="F26" s="26"/>
     </row>
     <row r="27" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A27" s="29" t="s">
+      <c r="A27" s="24" t="s">
         <v>27</v>
       </c>
-      <c r="B27" s="30"/>
-      <c r="C27" s="30"/>
-      <c r="D27" s="30"/>
-      <c r="E27" s="30"/>
-      <c r="F27" s="31"/>
+      <c r="B27" s="25"/>
+      <c r="C27" s="25"/>
+      <c r="D27" s="25"/>
+      <c r="E27" s="25"/>
+      <c r="F27" s="26"/>
     </row>
     <row r="28" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A28" s="29" t="s">
+      <c r="A28" s="24" t="s">
         <v>28</v>
       </c>
-      <c r="B28" s="30"/>
-      <c r="C28" s="30"/>
-      <c r="D28" s="30"/>
-      <c r="E28" s="30"/>
-      <c r="F28" s="31"/>
+      <c r="B28" s="25"/>
+      <c r="C28" s="25"/>
+      <c r="D28" s="25"/>
+      <c r="E28" s="25"/>
+      <c r="F28" s="26"/>
     </row>
     <row r="29" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A29" s="29" t="s">
+      <c r="A29" s="24" t="s">
         <v>15</v>
       </c>
-      <c r="B29" s="30"/>
-      <c r="C29" s="30"/>
-      <c r="D29" s="30"/>
-      <c r="E29" s="30"/>
-      <c r="F29" s="31"/>
+      <c r="B29" s="25"/>
+      <c r="C29" s="25"/>
+      <c r="D29" s="25"/>
+      <c r="E29" s="25"/>
+      <c r="F29" s="26"/>
     </row>
     <row r="30" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A30" s="29" t="s">
+      <c r="A30" s="24" t="s">
         <v>29</v>
       </c>
-      <c r="B30" s="30"/>
-      <c r="C30" s="30"/>
-      <c r="D30" s="30"/>
-      <c r="E30" s="30"/>
-      <c r="F30" s="31"/>
+      <c r="B30" s="25"/>
+      <c r="C30" s="25"/>
+      <c r="D30" s="25"/>
+      <c r="E30" s="25"/>
+      <c r="F30" s="26"/>
     </row>
     <row r="31" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A31" s="29" t="s">
+      <c r="A31" s="24" t="s">
         <v>30</v>
       </c>
-      <c r="B31" s="30"/>
-      <c r="C31" s="30"/>
-      <c r="D31" s="30"/>
-      <c r="E31" s="30"/>
-      <c r="F31" s="31"/>
+      <c r="B31" s="25"/>
+      <c r="C31" s="25"/>
+      <c r="D31" s="25"/>
+      <c r="E31" s="25"/>
+      <c r="F31" s="26"/>
     </row>
     <row r="32" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A32" s="8" t="s">
         <v>31</v>
       </c>
-      <c r="B32" s="9"/>
-      <c r="C32" s="9"/>
-      <c r="D32" s="9"/>
-      <c r="E32" s="9"/>
-      <c r="F32" s="10"/>
-    </row>
-    <row r="33" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A33" s="29" t="s">
+      <c r="F32" s="9"/>
+    </row>
+    <row r="33" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A33" s="24" t="s">
         <v>32</v>
       </c>
-      <c r="B33" s="30"/>
-      <c r="C33" s="30"/>
-      <c r="D33" s="30"/>
-      <c r="E33" s="30"/>
-      <c r="F33" s="31"/>
-    </row>
-    <row r="34" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A34" s="29" t="s">
+      <c r="B33" s="25"/>
+      <c r="C33" s="25"/>
+      <c r="D33" s="25"/>
+      <c r="E33" s="25"/>
+      <c r="F33" s="26"/>
+    </row>
+    <row r="34" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A34" s="24" t="s">
         <v>33</v>
       </c>
-      <c r="B34" s="30"/>
-      <c r="C34" s="30"/>
-      <c r="D34" s="30"/>
-      <c r="E34" s="30"/>
-      <c r="F34" s="31"/>
-    </row>
-    <row r="35" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A35" s="35" t="s">
+      <c r="B34" s="25"/>
+      <c r="C34" s="25"/>
+      <c r="D34" s="25"/>
+      <c r="E34" s="25"/>
+      <c r="F34" s="26"/>
+    </row>
+    <row r="35" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A35" s="34" t="s">
         <v>16</v>
       </c>
-      <c r="B35" s="36"/>
-      <c r="C35" s="36"/>
-      <c r="D35" s="36"/>
-      <c r="E35" s="36"/>
-      <c r="F35" s="37"/>
-    </row>
-    <row r="36" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A36" s="29" t="s">
+      <c r="B35" s="35"/>
+      <c r="C35" s="35"/>
+      <c r="D35" s="35"/>
+      <c r="E35" s="35"/>
+      <c r="F35" s="36"/>
+    </row>
+    <row r="36" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A36" s="24" t="s">
         <v>17</v>
       </c>
-      <c r="B36" s="30"/>
-      <c r="C36" s="30"/>
-      <c r="D36" s="30"/>
-      <c r="E36" s="30"/>
-      <c r="F36" s="31"/>
-    </row>
-    <row r="37" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A37" s="29" t="s">
+      <c r="B36" s="25"/>
+      <c r="C36" s="25"/>
+      <c r="D36" s="25"/>
+      <c r="E36" s="25"/>
+      <c r="F36" s="26"/>
+    </row>
+    <row r="37" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A37" s="24" t="s">
         <v>39</v>
       </c>
-      <c r="B37" s="30"/>
-      <c r="C37" s="30"/>
-      <c r="D37" s="30"/>
-      <c r="E37" s="30"/>
-      <c r="F37" s="31"/>
-    </row>
-    <row r="38" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A38" s="52" t="s">
+      <c r="B37" s="25"/>
+      <c r="C37" s="25"/>
+      <c r="D37" s="25"/>
+      <c r="E37" s="25"/>
+      <c r="F37" s="26"/>
+    </row>
+    <row r="38" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A38" s="43" t="s">
         <v>40</v>
       </c>
-      <c r="B38" s="53"/>
-      <c r="C38" s="53"/>
-      <c r="D38" s="53"/>
-      <c r="E38" s="53"/>
-      <c r="F38" s="54"/>
-    </row>
-    <row r="39" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A39" s="22" t="s">
+      <c r="B38" s="44"/>
+      <c r="C38" s="44"/>
+      <c r="D38" s="44"/>
+      <c r="E38" s="44"/>
+      <c r="F38" s="45"/>
+    </row>
+    <row r="39" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A39" s="21" t="s">
         <v>18</v>
       </c>
-      <c r="B39" s="21"/>
-      <c r="C39" s="21"/>
-      <c r="D39" s="21"/>
-      <c r="E39" s="21"/>
-      <c r="F39" s="21"/>
-      <c r="G39" s="9"/>
-    </row>
-    <row r="40" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B39" s="20"/>
+      <c r="C39" s="20"/>
+      <c r="D39" s="20"/>
+      <c r="E39" s="20"/>
+      <c r="F39" s="20"/>
+    </row>
+    <row r="40" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A40" s="5" t="s">
         <v>19</v>
       </c>
@@ -2900,41 +2785,41 @@
       <c r="C40" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="D40" s="25" t="s">
+      <c r="D40" s="27" t="s">
         <v>22</v>
       </c>
-      <c r="E40" s="26"/>
-      <c r="F40" s="19" t="s">
+      <c r="E40" s="28"/>
+      <c r="F40" s="18" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="41" spans="1:7" ht="40.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="41" spans="1:6" ht="40.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A41" s="6"/>
       <c r="B41" s="4"/>
       <c r="C41" s="4"/>
-      <c r="D41" s="27"/>
-      <c r="E41" s="32"/>
-      <c r="F41" s="33"/>
-    </row>
-    <row r="42" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="D41" s="29"/>
+      <c r="E41" s="31"/>
+      <c r="F41" s="32"/>
+    </row>
+    <row r="42" spans="1:6" ht="45" customHeight="1" x14ac:dyDescent="0.15">
       <c r="E42" s="7"/>
-      <c r="F42" s="34"/>
-    </row>
-    <row r="43" spans="1:7" ht="22.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="44" spans="1:7" ht="22.5" customHeight="1" x14ac:dyDescent="0.15"/>
+      <c r="F42" s="33"/>
+    </row>
+    <row r="43" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="44" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.15"/>
   </sheetData>
   <mergeCells count="34">
-    <mergeCell ref="D11:F11"/>
     <mergeCell ref="A3:F3"/>
     <mergeCell ref="A15:B16"/>
     <mergeCell ref="A17:B17"/>
     <mergeCell ref="A18:A19"/>
     <mergeCell ref="C15:F15"/>
     <mergeCell ref="D9:F9"/>
-    <mergeCell ref="A38:F38"/>
-    <mergeCell ref="A29:F29"/>
-    <mergeCell ref="A30:F30"/>
-    <mergeCell ref="A31:F31"/>
+    <mergeCell ref="A34:F34"/>
+    <mergeCell ref="C16:F16"/>
+    <mergeCell ref="C17:F17"/>
+    <mergeCell ref="C18:F18"/>
+    <mergeCell ref="D11:F11"/>
     <mergeCell ref="D10:F10"/>
     <mergeCell ref="A28:F28"/>
     <mergeCell ref="B22:F22"/>
@@ -2942,11 +2827,6 @@
     <mergeCell ref="A25:F25"/>
     <mergeCell ref="C19:F19"/>
     <mergeCell ref="C21:D21"/>
-    <mergeCell ref="A33:F33"/>
-    <mergeCell ref="A34:F34"/>
-    <mergeCell ref="C16:F16"/>
-    <mergeCell ref="C17:F17"/>
-    <mergeCell ref="C18:F18"/>
     <mergeCell ref="A26:F26"/>
     <mergeCell ref="D40:E40"/>
     <mergeCell ref="E23:F23"/>
@@ -2958,6 +2838,11 @@
     <mergeCell ref="A37:F37"/>
     <mergeCell ref="A20:A23"/>
     <mergeCell ref="C20:F20"/>
+    <mergeCell ref="A38:F38"/>
+    <mergeCell ref="A29:F29"/>
+    <mergeCell ref="A30:F30"/>
+    <mergeCell ref="A31:F31"/>
+    <mergeCell ref="A33:F33"/>
   </mergeCells>
   <phoneticPr fontId="2"/>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
